--- a/question/Question.xlsx
+++ b/question/Question.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\8-3\minigame\question\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\file_luu_tru\du_an\minigame\question\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08477153-C5CD-4B14-BBDE-B40F5208AFFB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6EABAC-A16E-440C-9F9B-F6E02B1457CF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5268" xr2:uid="{13D47C2E-6DA5-4663-B107-8F3B884F698D}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="65">
   <si>
     <t>question</t>
   </si>
@@ -78,9 +78,6 @@
     <t>Nhà giáo</t>
   </si>
   <si>
-    <t>Tình yêu</t>
-  </si>
-  <si>
     <t>fill</t>
   </si>
   <si>
@@ -105,9 +102,6 @@
     <t>guy</t>
   </si>
   <si>
-    <t>Voi chín ngà, gà chín cựa, ngựa….</t>
-  </si>
-  <si>
     <t>Cắt đầu moi</t>
   </si>
   <si>
@@ -144,13 +138,88 @@
     <t>M10</t>
   </si>
   <si>
-    <t>Hai không Hai bốn ??? Câu sau viết ra số như thế nào</t>
-  </si>
-  <si>
-    <t>0044</t>
-  </si>
-  <si>
     <t>9 cẳng</t>
+  </si>
+  <si>
+    <t>sound</t>
+  </si>
+  <si>
+    <t>Tôi không sợ người học 10 000 cú đá mà tôi chỉ sợ ____</t>
+  </si>
+  <si>
+    <t>Voi chín ngà, gà chín cựa, ngựa___</t>
+  </si>
+  <si>
+    <t>Họ đá tôi</t>
+  </si>
+  <si>
+    <t>người học 10 000 cú đấm</t>
+  </si>
+  <si>
+    <t>cuda.jpg</t>
+  </si>
+  <si>
+    <t>người học 1 cú đá 10 000 lần</t>
+  </si>
+  <si>
+    <t>Đúng</t>
+  </si>
+  <si>
+    <t>Lịch sử Quang Trung và Nguyễn Huệ là ???</t>
+  </si>
+  <si>
+    <t>anh em ruột</t>
+  </si>
+  <si>
+    <t>lichsu.jpg</t>
+  </si>
+  <si>
+    <t>Bạn bè</t>
+  </si>
+  <si>
+    <t>đối tác làm ăn</t>
+  </si>
+  <si>
+    <t>Valentine</t>
+  </si>
+  <si>
+    <t>Trả lời 'Đúng': 1 - 5 + (7 x 10) = ??</t>
+  </si>
+  <si>
+    <t>hoc_thay.mp4</t>
+  </si>
+  <si>
+    <t>Học thầy không tày học bạn</t>
+  </si>
+  <si>
+    <t>Không thầy đố mày làm nên</t>
+  </si>
+  <si>
+    <t>Làm thầy mày không nên đố</t>
+  </si>
+  <si>
+    <t>36 kế chạy là thượng sách</t>
+  </si>
+  <si>
+    <t>đây là câu gì ??</t>
+  </si>
+  <si>
+    <t>tinh_dep_den_may_cung_tan.mp3</t>
+  </si>
+  <si>
+    <t>Đoạn nhạc sau là lời bài hát nào??</t>
+  </si>
+  <si>
+    <t>Tình đẹp đến mấy cũng tàn</t>
+  </si>
+  <si>
+    <t>Ngày ấy</t>
+  </si>
+  <si>
+    <t>Ký ức không màu</t>
+  </si>
+  <si>
+    <t>Sai người sai thời điểm</t>
   </si>
 </sst>
 </file>
@@ -194,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -205,7 +274,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,10 +588,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6D20C5-F5C4-4FB0-8774-1BDFC45A7A57}">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -540,34 +608,37 @@
         <v>9</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -582,28 +653,29 @@
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="K2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="2">
+      <c r="M2" s="2">
         <v>5</v>
       </c>
-      <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" s="1"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
@@ -612,29 +684,30 @@
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="2">
+      <c r="K3" s="1"/>
+      <c r="L3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="2">
         <v>5</v>
       </c>
-      <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" s="1"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A51" si="0">A3+1</f>
         <v>3</v>
@@ -646,32 +719,33 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="1"/>
+      <c r="H4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="2">
+      <c r="M4" s="2">
         <v>5</v>
       </c>
-      <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O4" s="1"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -680,29 +754,30 @@
         <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="2">
+      <c r="K5" s="1"/>
+      <c r="L5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="2">
         <v>5</v>
       </c>
-      <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O5" s="1"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -716,25 +791,28 @@
       <c r="D6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6">
-        <v>2024</v>
-      </c>
-      <c r="I6">
-        <v>2044</v>
-      </c>
-      <c r="J6">
-        <v>24</v>
-      </c>
-      <c r="L6" s="2">
-        <v>0</v>
-      </c>
-      <c r="M6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="2">
+        <v>5</v>
+      </c>
       <c r="N6" s="1"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O6" s="1"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -743,15 +821,36 @@
         <v>11</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" s="2">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2">
         <v>5</v>
       </c>
-      <c r="M7" s="1"/>
       <c r="N7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O7" s="1"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -760,15 +859,21 @@
         <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" s="2">
+        <v>17</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8" s="2">
         <v>5</v>
       </c>
-      <c r="M8" s="1"/>
       <c r="N8" s="1"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8" s="1"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -779,13 +884,34 @@
       <c r="C9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="2">
+      <c r="D9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M9" s="2">
         <v>5</v>
       </c>
-      <c r="M9" s="1"/>
       <c r="N9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9" s="1"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -796,13 +922,34 @@
       <c r="C10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L10" s="2">
+      <c r="D10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K10" t="s">
+        <v>64</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" s="2">
         <v>5</v>
       </c>
-      <c r="M10" s="1"/>
       <c r="N10" s="1"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -813,13 +960,13 @@
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L11" s="2">
+      <c r="M11" s="2">
         <v>5</v>
       </c>
-      <c r="M11" s="1"/>
       <c r="N11" s="1"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -830,13 +977,13 @@
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L12" s="2">
+      <c r="M12" s="2">
         <v>5</v>
       </c>
-      <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -847,13 +994,13 @@
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L13" s="2">
-        <v>10</v>
-      </c>
-      <c r="M13" s="1"/>
+      <c r="M13" s="2">
+        <v>10</v>
+      </c>
       <c r="N13" s="1"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O13" s="1"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -864,13 +1011,13 @@
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L14" s="2">
-        <v>10</v>
-      </c>
-      <c r="M14" s="1"/>
+      <c r="M14" s="2">
+        <v>10</v>
+      </c>
       <c r="N14" s="1"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O14" s="1"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -881,11 +1028,11 @@
       <c r="C15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L15" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M15" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -896,562 +1043,562 @@
       <c r="C16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L16" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M16" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M18" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M19" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L17" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="B20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M20" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M21" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M22" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M23" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M24" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M25" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M26" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M27" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M28" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M29" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M30" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M31" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M32" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M33" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M34" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M35" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M36" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M37" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M38" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M39" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M40" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L18" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M41" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L19" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <f t="shared" si="0"/>
+      <c r="C42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M42" s="2">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>10</v>
+      </c>
+      <c r="O42">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s">
+        <v>32</v>
+      </c>
+      <c r="H43" t="s">
+        <v>33</v>
+      </c>
+      <c r="I43" t="s">
+        <v>34</v>
+      </c>
+      <c r="J43" t="s">
+        <v>35</v>
+      </c>
+      <c r="K43" t="s">
+        <v>36</v>
+      </c>
+      <c r="L43" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="2">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>15</v>
+      </c>
+      <c r="O43">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L20" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="C44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M44" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L21" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M45" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L22" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="C46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M46" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L23" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="C47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M47" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L24" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="B25" s="1" t="s">
+      <c r="C48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M48" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L25" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B26" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M49" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L26" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M50" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L27" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L28" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L29" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L30" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L31" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L32" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L33" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L34" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L35" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L36" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L37" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L38" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L39" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L40" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L41" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L42" s="2">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>10</v>
-      </c>
-      <c r="N42">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" t="s">
-        <v>34</v>
-      </c>
-      <c r="G43" t="s">
-        <v>35</v>
-      </c>
-      <c r="H43" t="s">
-        <v>36</v>
-      </c>
-      <c r="I43" t="s">
-        <v>37</v>
-      </c>
-      <c r="J43" t="s">
-        <v>38</v>
-      </c>
-      <c r="K43" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="2">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>15</v>
-      </c>
-      <c r="N43">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L44" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L45" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L46" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L47" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L48" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L49" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L50" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C51" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L51" s="2">
+      <c r="M51" s="2">
         <v>0</v>
       </c>
     </row>

--- a/question/Question.xlsx
+++ b/question/Question.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\file_luu_tru\du_an\minigame\question\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6EABAC-A16E-440C-9F9B-F6E02B1457CF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0C8BB6-FB23-4F0B-A4E3-301335E38B3B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5268" xr2:uid="{13D47C2E-6DA5-4663-B107-8F3B884F698D}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="107">
   <si>
     <t>question</t>
   </si>
@@ -138,9 +138,6 @@
     <t>M10</t>
   </si>
   <si>
-    <t>9 cẳng</t>
-  </si>
-  <si>
     <t>sound</t>
   </si>
   <si>
@@ -220,6 +217,148 @@
   </si>
   <si>
     <t>Sai người sai thời điểm</t>
+  </si>
+  <si>
+    <t>explanation</t>
+  </si>
+  <si>
+    <t>explanation_image</t>
+  </si>
+  <si>
+    <t>Ngày 8/3 là Ngày Quốc tế Phụ nữ, tôn vinh phụ nữ trên toàn thế giới.</t>
+  </si>
+  <si>
+    <t>Găng tay vàng trong làng bắt gôn là ??</t>
+  </si>
+  <si>
+    <t>Trương Công Hiện</t>
+  </si>
+  <si>
+    <t>Nguyễn Phương Nguyên</t>
+  </si>
+  <si>
+    <t>Hà Nguyên Vũ</t>
+  </si>
+  <si>
+    <t>Nguyễn Như Quang</t>
+  </si>
+  <si>
+    <t>Phải đọc kĩ nhé. Yêu cầu trả lời ĐÚNG =)))</t>
+  </si>
+  <si>
+    <t>Bà Triệu</t>
+  </si>
+  <si>
+    <t>Hai Bà Trưng</t>
+  </si>
+  <si>
+    <t>Võ Thị Sáu</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Minh Khai</t>
+  </si>
+  <si>
+    <t>Hai Bà Trưng lãnh đạo cuộc khởi nghĩa năm 40 chống nhà Hán, thể hiện tinh thần anh hùng và vai trò to lớn của phụ nữ Việt Nam trong lịch sử.</t>
+  </si>
+  <si>
+    <t>ngua_cat_dau_moi.jpg</t>
+  </si>
+  <si>
+    <t>Tưởng là ngựa cắt đầu moi không đấy =))))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không được nhầm là anh em đâu nhé </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Câu thành ngữ nào thể hiện </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tinh thần mạnh mẽ, kiên cường của phụ nữ Việt Nam?</t>
+    </r>
+  </si>
+  <si>
+    <t>Công cha như núi Thái Sơn</t>
+  </si>
+  <si>
+    <t>Giặc đến nhà đàn bà cũng đánh</t>
+  </si>
+  <si>
+    <t>Đèn nhà ai nhà nấy rạng</t>
+  </si>
+  <si>
+    <t>Ăn quả nhớ kẻ trồng cây</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 cây làm chẳng nên non 3 cây chụm lại </t>
+  </si>
+  <si>
+    <t>nên hòn núi cao</t>
+  </si>
+  <si>
+    <t>thì thừa 2 cây</t>
+  </si>
+  <si>
+    <t>vẫn là 3 cây</t>
+  </si>
+  <si>
+    <t>Càng đọc càng thấy tào lao, cây làm nên núi thì tao chết liền</t>
+  </si>
+  <si>
+    <t>Người tính không bằng</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>Trời tính</t>
+  </si>
+  <si>
+    <t>Máy tính</t>
+  </si>
+  <si>
+    <t>Có công mài sắt</t>
+  </si>
+  <si>
+    <t>Có ngày nên kim</t>
+  </si>
+  <si>
+    <t>Có ngày tháng năm</t>
+  </si>
+  <si>
+    <t>Có ngày mỏi tay</t>
+  </si>
+  <si>
+    <t>Ngựa ít thôi</t>
+  </si>
+  <si>
+    <t>Đây là câu ???</t>
+  </si>
+  <si>
+    <t>Thắng làm vua thua làm giặc</t>
+  </si>
+  <si>
+    <t>99% con bạc dừng lại trước khi thắng lớn</t>
+  </si>
+  <si>
+    <t>Da màu không mạnh bằng Daden</t>
+  </si>
+  <si>
+    <t>Tốt gỗ hơn tốt nước sơn</t>
+  </si>
+  <si>
+    <t>go_son.mp4</t>
+  </si>
+  <si>
+    <t>Ở Việt Nam, 8/3 còn gắn với cuộc khởi nghĩa nào?</t>
   </si>
 </sst>
 </file>
@@ -263,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -274,6 +413,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -588,10 +728,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6D20C5-F5C4-4FB0-8774-1BDFC45A7A57}">
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -608,7 +748,7 @@
         <v>9</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>10</v>
@@ -637,8 +777,14 @@
       <c r="O1" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -664,7 +810,7 @@
         <v>16</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>1</v>
@@ -674,8 +820,11 @@
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
@@ -707,7 +856,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A51" si="0">A3+1</f>
         <v>3</v>
@@ -719,9 +868,11 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
@@ -731,7 +882,7 @@
         <v>26</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>27</v>
@@ -744,8 +895,11 @@
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -777,7 +931,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -789,19 +943,19 @@
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>3</v>
@@ -812,7 +966,7 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -824,22 +978,22 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" t="s">
         <v>49</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K7" t="s">
-        <v>50</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>1</v>
@@ -849,8 +1003,11 @@
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -862,18 +1019,21 @@
         <v>17</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -885,22 +1045,22 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
         <v>53</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" t="s">
         <v>55</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K9" t="s">
-        <v>56</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>2</v>
@@ -911,7 +1071,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -923,22 +1083,22 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" t="s">
         <v>60</v>
       </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="I10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" t="s">
         <v>63</v>
-      </c>
-      <c r="K10" t="s">
-        <v>64</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>1</v>
@@ -949,7 +1109,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -960,13 +1120,34 @@
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D11" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" t="s">
+        <v>76</v>
+      </c>
+      <c r="L11" t="s">
+        <v>2</v>
+      </c>
       <c r="M11" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -977,13 +1158,31 @@
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J12" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="M12" s="2">
         <v>5</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -994,13 +1193,28 @@
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D13" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" t="s">
+        <v>94</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="M13" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1011,13 +1225,28 @@
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" t="s">
+        <v>96</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J14" t="s">
+        <v>98</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="M14" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1028,11 +1257,32 @@
       <c r="C15" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" t="s">
+        <v>105</v>
+      </c>
+      <c r="H15" t="s">
+        <v>101</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J15" t="s">
+        <v>103</v>
+      </c>
+      <c r="K15" t="s">
+        <v>104</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="M15" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1043,6 +1293,24 @@
       <c r="C16" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D16" t="s">
+        <v>81</v>
+      </c>
+      <c r="H16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I16" t="s">
+        <v>83</v>
+      </c>
+      <c r="J16" t="s">
+        <v>84</v>
+      </c>
+      <c r="K16" t="s">
+        <v>85</v>
+      </c>
+      <c r="L16" t="s">
+        <v>2</v>
+      </c>
       <c r="M16" s="2">
         <v>10</v>
       </c>
@@ -1436,12 +1704,6 @@
       <c r="M42" s="2">
         <v>0</v>
       </c>
-      <c r="N42">
-        <v>10</v>
-      </c>
-      <c r="O42">
-        <v>20</v>
-      </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
@@ -1508,8 +1770,32 @@
       <c r="C45" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D45" t="s">
+        <v>67</v>
+      </c>
+      <c r="H45" t="s">
+        <v>68</v>
+      </c>
+      <c r="I45" t="s">
+        <v>69</v>
+      </c>
+      <c r="J45" t="s">
+        <v>70</v>
+      </c>
+      <c r="K45" t="s">
+        <v>71</v>
+      </c>
+      <c r="L45" t="s">
+        <v>4</v>
+      </c>
       <c r="M45" s="2">
         <v>0</v>
+      </c>
+      <c r="N45">
+        <v>10</v>
+      </c>
+      <c r="O45">
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">

--- a/question/Question.xlsx
+++ b/question/Question.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\file_luu_tru\du_an\minigame\question\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0C8BB6-FB23-4F0B-A4E3-301335E38B3B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E237A35-13AB-40D5-96AD-1B3D0CE6846C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5268" xr2:uid="{13D47C2E-6DA5-4663-B107-8F3B884F698D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{13D47C2E-6DA5-4663-B107-8F3B884F698D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="133">
   <si>
     <t>question</t>
   </si>
@@ -359,6 +370,84 @@
   </si>
   <si>
     <t>Ở Việt Nam, 8/3 còn gắn với cuộc khởi nghĩa nào?</t>
+  </si>
+  <si>
+    <t>Đây là giọng của dân tộc nào ???</t>
+  </si>
+  <si>
+    <t>Khô gà được làm từ ??</t>
+  </si>
+  <si>
+    <t>Bã mía</t>
+  </si>
+  <si>
+    <t>Ức gà</t>
+  </si>
+  <si>
+    <t>Bã sắn dây</t>
+  </si>
+  <si>
+    <t>Bìa carton</t>
+  </si>
+  <si>
+    <t>chua_tay_dau.mp3</t>
+  </si>
+  <si>
+    <t>Dân tộc Nùng</t>
+  </si>
+  <si>
+    <t>Dân tộc Chăm</t>
+  </si>
+  <si>
+    <t>Dân tộc Kinh</t>
+  </si>
+  <si>
+    <t>Dân tộc Tày</t>
+  </si>
+  <si>
+    <t>vu_a_vu.png</t>
+  </si>
+  <si>
+    <t>Alo Vũ à Vũ</t>
+  </si>
+  <si>
+    <t>Con gái nói không sao đâu có nghĩa là gì ???</t>
+  </si>
+  <si>
+    <t>Thật sự không sao</t>
+  </si>
+  <si>
+    <t>Đang rất sao</t>
+  </si>
+  <si>
+    <t>Muốn nói chuyện</t>
+  </si>
+  <si>
+    <t>Muốn ăn</t>
+  </si>
+  <si>
+    <t>kho_ga.jpg</t>
+  </si>
+  <si>
+    <t>Sa Vào Nguy Hiểm _ 悬溺 (mp3cut.net).mp3</t>
+  </si>
+  <si>
+    <t>Nghe nhạc đoán tên</t>
+  </si>
+  <si>
+    <t>悬溺</t>
+  </si>
+  <si>
+    <t>lao vào nguy hiểm</t>
+  </si>
+  <si>
+    <t>Rushing into danger</t>
+  </si>
+  <si>
+    <t>Nhạc trung thì phải tên Trung roi</t>
+  </si>
+  <si>
+    <t>รีบเร่งเข้าสู่อันตราย</t>
   </si>
 </sst>
 </file>
@@ -402,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -413,7 +502,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -432,9 +522,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -472,7 +562,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -578,7 +668,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -720,7 +810,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -730,6 +820,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6D20C5-F5C4-4FB0-8774-1BDFC45A7A57}">
   <dimension ref="A1:Q51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="8.88671875" style="5"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
@@ -820,7 +913,7 @@
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
-      <c r="P2" t="s">
+      <c r="P2" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -895,7 +988,7 @@
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-      <c r="P4" t="s">
+      <c r="P4" s="5" t="s">
         <v>79</v>
       </c>
     </row>
@@ -980,10 +1073,10 @@
       <c r="D7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="5">
         <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -992,7 +1085,7 @@
       <c r="J7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="5" t="s">
         <v>49</v>
       </c>
       <c r="L7" s="1" t="s">
@@ -1003,7 +1096,7 @@
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="P7" t="s">
+      <c r="P7" s="5" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1021,7 +1114,7 @@
       <c r="D8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="5" t="s">
         <v>44</v>
       </c>
       <c r="M8" s="2">
@@ -1029,7 +1122,7 @@
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-      <c r="P8" t="s">
+      <c r="P8" s="5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1047,10 +1140,10 @@
       <c r="D9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="5" t="s">
         <v>53</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -1059,7 +1152,7 @@
       <c r="J9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="5" t="s">
         <v>55</v>
       </c>
       <c r="L9" s="1" t="s">
@@ -1085,10 +1178,10 @@
       <c r="D10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="5" t="s">
         <v>60</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -1097,7 +1190,7 @@
       <c r="J10" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="5" t="s">
         <v>63</v>
       </c>
       <c r="L10" s="1" t="s">
@@ -1120,22 +1213,22 @@
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="5" t="s">
         <v>2</v>
       </c>
       <c r="M11" s="2">
@@ -1143,7 +1236,7 @@
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-      <c r="P11" t="s">
+      <c r="P11" s="5" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1161,13 +1254,13 @@
       <c r="D12" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="5" t="s">
         <v>88</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="5" t="s">
         <v>87</v>
       </c>
       <c r="L12" s="1" t="s">
@@ -1178,7 +1271,7 @@
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-      <c r="P12" t="s">
+      <c r="P12" s="5" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1196,13 +1289,13 @@
       <c r="D13" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="5" t="s">
         <v>92</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="5" t="s">
         <v>94</v>
       </c>
       <c r="L13" s="1" t="s">
@@ -1228,13 +1321,13 @@
       <c r="D14" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="5" t="s">
         <v>96</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="5" t="s">
         <v>98</v>
       </c>
       <c r="L14" s="1" t="s">
@@ -1260,19 +1353,19 @@
       <c r="D15" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="5" t="s">
         <v>101</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="5" t="s">
         <v>104</v>
       </c>
       <c r="L15" s="1" t="s">
@@ -1293,29 +1386,29 @@
       <c r="C16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L16" s="5" t="s">
         <v>2</v>
       </c>
       <c r="M16" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1326,11 +1419,26 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
       <c r="M17" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1341,11 +1449,26 @@
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H18" s="5">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0</v>
+      </c>
       <c r="M18" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1356,11 +1479,35 @@
       <c r="C19" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D19" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>1</v>
+      </c>
       <c r="M19" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P19" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1371,11 +1518,26 @@
       <c r="C20" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H20" s="5">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0</v>
+      </c>
       <c r="M20" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1386,11 +1548,26 @@
       <c r="C21" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H21" s="5">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5">
+        <v>0</v>
+      </c>
       <c r="M21" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1401,11 +1578,26 @@
       <c r="C22" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H22" s="5">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0</v>
+      </c>
       <c r="M22" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1416,11 +1608,38 @@
       <c r="C23" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D23" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>1</v>
+      </c>
       <c r="M23" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P23" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1431,11 +1650,26 @@
       <c r="C24" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H24" s="5">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5">
+        <v>0</v>
+      </c>
       <c r="M24" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1446,11 +1680,26 @@
       <c r="C25" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H25" s="5">
+        <v>0</v>
+      </c>
+      <c r="I25" s="5">
+        <v>0</v>
+      </c>
+      <c r="J25" s="5">
+        <v>0</v>
+      </c>
+      <c r="K25" s="5">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5">
+        <v>0</v>
+      </c>
       <c r="M25" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -1461,11 +1710,26 @@
       <c r="C26" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H26" s="5">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5">
+        <v>0</v>
+      </c>
+      <c r="K26" s="5">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5">
+        <v>0</v>
+      </c>
       <c r="M26" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -1476,11 +1740,26 @@
       <c r="C27" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H27" s="5">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5">
+        <v>0</v>
+      </c>
+      <c r="K27" s="5">
+        <v>0</v>
+      </c>
+      <c r="L27" s="5">
+        <v>0</v>
+      </c>
       <c r="M27" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -1491,11 +1770,26 @@
       <c r="C28" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H28" s="5">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5">
+        <v>0</v>
+      </c>
+      <c r="L28" s="5">
+        <v>0</v>
+      </c>
       <c r="M28" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1506,11 +1800,26 @@
       <c r="C29" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H29" s="5">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5">
+        <v>0</v>
+      </c>
+      <c r="J29" s="5">
+        <v>0</v>
+      </c>
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5">
+        <v>0</v>
+      </c>
       <c r="M29" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -1521,11 +1830,32 @@
       <c r="C30" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D30" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="M30" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1536,11 +1866,26 @@
       <c r="C31" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H31" s="5">
+        <v>0</v>
+      </c>
+      <c r="I31" s="5">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5">
+        <v>0</v>
+      </c>
+      <c r="K31" s="5">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5">
+        <v>0</v>
+      </c>
       <c r="M31" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -1551,6 +1896,21 @@
       <c r="C32" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H32" s="5">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5">
+        <v>0</v>
+      </c>
       <c r="M32" s="2">
         <v>10</v>
       </c>
@@ -1566,6 +1926,21 @@
       <c r="C33" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H33" s="5">
+        <v>0</v>
+      </c>
+      <c r="I33" s="5">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5">
+        <v>0</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <v>0</v>
+      </c>
       <c r="M33" s="2">
         <v>10</v>
       </c>
@@ -1581,6 +1956,21 @@
       <c r="C34" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H34" s="5">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
+        <v>0</v>
+      </c>
       <c r="M34" s="2">
         <v>10</v>
       </c>
@@ -1596,6 +1986,21 @@
       <c r="C35" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H35" s="5">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5">
+        <v>0</v>
+      </c>
+      <c r="J35" s="5">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5">
+        <v>0</v>
+      </c>
       <c r="M35" s="2">
         <v>10</v>
       </c>
@@ -1611,6 +2016,21 @@
       <c r="C36" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H36" s="5">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5">
+        <v>0</v>
+      </c>
       <c r="M36" s="2">
         <v>10</v>
       </c>
@@ -1626,6 +2046,21 @@
       <c r="C37" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H37" s="5">
+        <v>0</v>
+      </c>
+      <c r="I37" s="5">
+        <v>0</v>
+      </c>
+      <c r="J37" s="5">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5">
+        <v>0</v>
+      </c>
       <c r="M37" s="2">
         <v>10</v>
       </c>
@@ -1641,6 +2076,21 @@
       <c r="C38" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H38" s="5">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
+        <v>0</v>
+      </c>
       <c r="M38" s="2">
         <v>10</v>
       </c>
@@ -1656,6 +2106,21 @@
       <c r="C39" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H39" s="5">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5">
+        <v>0</v>
+      </c>
+      <c r="J39" s="5">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5">
+        <v>0</v>
+      </c>
       <c r="M39" s="2">
         <v>10</v>
       </c>
@@ -1671,6 +2136,21 @@
       <c r="C40" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H40" s="5">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5">
+        <v>0</v>
+      </c>
       <c r="M40" s="2">
         <v>10</v>
       </c>
@@ -1686,6 +2166,21 @@
       <c r="C41" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H41" s="5">
+        <v>0</v>
+      </c>
+      <c r="I41" s="5">
+        <v>0</v>
+      </c>
+      <c r="J41" s="5">
+        <v>0</v>
+      </c>
+      <c r="K41" s="5">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5">
+        <v>0</v>
+      </c>
       <c r="M41" s="2">
         <v>0</v>
       </c>
@@ -1701,6 +2196,21 @@
       <c r="C42" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H42" s="5">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5">
+        <v>0</v>
+      </c>
       <c r="M42" s="2">
         <v>0</v>
       </c>
@@ -1716,31 +2226,31 @@
       <c r="C43" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J43" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K43" t="s">
+      <c r="K43" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L43" t="s">
+      <c r="L43" s="5" t="s">
         <v>3</v>
       </c>
       <c r="M43" s="2">
         <v>0</v>
       </c>
-      <c r="N43">
+      <c r="N43" s="5">
         <v>15</v>
       </c>
-      <c r="O43">
+      <c r="O43" s="5">
         <v>25</v>
       </c>
     </row>
@@ -1755,6 +2265,21 @@
       <c r="C44" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H44" s="5">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5">
+        <v>0</v>
+      </c>
+      <c r="J44" s="5">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5">
+        <v>0</v>
+      </c>
       <c r="M44" s="2">
         <v>0</v>
       </c>
@@ -1770,31 +2295,31 @@
       <c r="C45" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="J45" t="s">
+      <c r="J45" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="K45" t="s">
+      <c r="K45" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="L45" t="s">
+      <c r="L45" s="5" t="s">
         <v>4</v>
       </c>
       <c r="M45" s="2">
         <v>0</v>
       </c>
-      <c r="N45">
-        <v>10</v>
-      </c>
-      <c r="O45">
+      <c r="N45" s="5">
+        <v>10</v>
+      </c>
+      <c r="O45" s="5">
         <v>15</v>
       </c>
     </row>
@@ -1809,6 +2334,21 @@
       <c r="C46" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H46" s="5">
+        <v>0</v>
+      </c>
+      <c r="I46" s="5">
+        <v>0</v>
+      </c>
+      <c r="J46" s="5">
+        <v>0</v>
+      </c>
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5">
+        <v>0</v>
+      </c>
       <c r="M46" s="2">
         <v>0</v>
       </c>
@@ -1824,6 +2364,21 @@
       <c r="C47" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H47" s="5">
+        <v>0</v>
+      </c>
+      <c r="I47" s="5">
+        <v>0</v>
+      </c>
+      <c r="J47" s="5">
+        <v>0</v>
+      </c>
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5">
+        <v>0</v>
+      </c>
       <c r="M47" s="2">
         <v>0</v>
       </c>
@@ -1839,6 +2394,21 @@
       <c r="C48" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H48" s="5">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5">
+        <v>0</v>
+      </c>
+      <c r="K48" s="5">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5">
+        <v>0</v>
+      </c>
       <c r="M48" s="2">
         <v>0</v>
       </c>
@@ -1854,6 +2424,21 @@
       <c r="C49" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H49" s="5">
+        <v>0</v>
+      </c>
+      <c r="I49" s="5">
+        <v>0</v>
+      </c>
+      <c r="J49" s="5">
+        <v>0</v>
+      </c>
+      <c r="K49" s="5">
+        <v>0</v>
+      </c>
+      <c r="L49" s="5">
+        <v>0</v>
+      </c>
       <c r="M49" s="2">
         <v>0</v>
       </c>
@@ -1869,6 +2454,21 @@
       <c r="C50" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H50" s="5">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5">
+        <v>0</v>
+      </c>
       <c r="M50" s="2">
         <v>0</v>
       </c>
@@ -1883,6 +2483,21 @@
       </c>
       <c r="C51" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H51" t="s">
+        <v>121</v>
+      </c>
+      <c r="I51" t="s">
+        <v>122</v>
+      </c>
+      <c r="J51" t="s">
+        <v>123</v>
+      </c>
+      <c r="K51" t="s">
+        <v>124</v>
       </c>
       <c r="M51" s="2">
         <v>0</v>

--- a/question/Question.xlsx
+++ b/question/Question.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\file_luu_tru\du_an\minigame\question\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E237A35-13AB-40D5-96AD-1B3D0CE6846C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB780B9-045B-480E-A6D0-FD42C5200A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{13D47C2E-6DA5-4663-B107-8F3B884F698D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="242">
   <si>
     <t>question</t>
   </si>
@@ -449,12 +449,672 @@
   <si>
     <t>รีบเร่งเข้าสู่อันตราย</t>
   </si>
+  <si>
+    <t>Thành phố nào được gọi là "thành phố ngàn hoa" ở Việt Nam ?</t>
+  </si>
+  <si>
+    <t>Buôn Ma Thuột</t>
+  </si>
+  <si>
+    <t>Đà Lạt</t>
+  </si>
+  <si>
+    <t>Nha Trang</t>
+  </si>
+  <si>
+    <t>Hải phòng</t>
+  </si>
+  <si>
+    <t>dalat.jpg</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Đà Lạt được mệnh danh là </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thành phố hoa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vì khí hậu mát mẻ quanh năm và có rất nhiều loài hoa đẹp nở khắp nơi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cao Lầu</t>
+  </si>
+  <si>
+    <t>Bánh Căn</t>
+  </si>
+  <si>
+    <t>Bún Bò</t>
+  </si>
+  <si>
+    <t>Phở sốt vang</t>
+  </si>
+  <si>
+    <t>Món ăn nào là đặc sản Hội An ?</t>
+  </si>
+  <si>
+    <t>Cao lầu là món đặc sản nổi tiếng của Hội An.</t>
+  </si>
+  <si>
+    <t>caolau.jpg</t>
+  </si>
+  <si>
+    <t>Orange.mp3</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Pink</t>
+  </si>
+  <si>
+    <t>Bài hát Orange của nhóm 7!! là một ca khúc J-Pop nhẹ nhàng, mang giai điệu trong trẻo và cảm xúc về tình bạn, tuổi trẻ và những kỷ niệm không thể quên.</t>
+  </si>
+  <si>
+    <t>Đây là bài ???</t>
+  </si>
+  <si>
+    <t>camconku.mp3</t>
+  </si>
+  <si>
+    <t>Nhạc này tên là ???</t>
+  </si>
+  <si>
+    <t>Nghiệp của tao</t>
+  </si>
+  <si>
+    <t>Sự nghiệp chướng</t>
+  </si>
+  <si>
+    <t>Đời chơi dell đẹp</t>
+  </si>
+  <si>
+    <t>Hận</t>
+  </si>
+  <si>
+    <t>AI đoán đúng ko =)))</t>
+  </si>
+  <si>
+    <t>Đèo Hải Vân Nối hai tỉnh nào??</t>
+  </si>
+  <si>
+    <t>Quảng Bình - Hà Tĩnh</t>
+  </si>
+  <si>
+    <t>Nha Trang - Đà Lạt</t>
+  </si>
+  <si>
+    <t>Bình Dương - Sài Gòn</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Đèo Hải Vân </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dài đến mức như nối liền cả hai vùng trời của Đà Nẵng và Thừa Thiên Huế.</t>
+    </r>
+  </si>
+  <si>
+    <t>haivan.jpg</t>
+  </si>
+  <si>
+    <t>Trái nào thướng được dùng làm thạch rau câu tự nhiên??</t>
+  </si>
+  <si>
+    <t>Dừa</t>
+  </si>
+  <si>
+    <t>Xoài</t>
+  </si>
+  <si>
+    <t>Nha đam</t>
+  </si>
+  <si>
+    <t>Dưa hấu</t>
+  </si>
+  <si>
+    <t>Dưa hấu ban đầu có màu gì</t>
+  </si>
+  <si>
+    <t>Màu Trắng</t>
+  </si>
+  <si>
+    <t>Màu Vàng</t>
+  </si>
+  <si>
+    <t>Màu Đỏ</t>
+  </si>
+  <si>
+    <t>Màu Xanh lá</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dừa thường được dùng để làm </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thạch rau câu tự nhiên</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vì nước dừa có vị ngọt mát.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trước đây dưa hấu hoang dại ở châu Phi thường có </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>màu nhạt hoặc vàng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, vị không ngọt. Khi được trồng và chọn giống qua nhiều thế hệ, ruột dưa dần </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>đỏ hơn và ngọt hơn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>duahau.jpg</t>
+  </si>
+  <si>
+    <t>dua.jpg</t>
+  </si>
+  <si>
+    <t>Khế</t>
+  </si>
+  <si>
+    <t>Chanh</t>
+  </si>
+  <si>
+    <t>Quất</t>
+  </si>
+  <si>
+    <t>Sầu riêng</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Chanh giúp </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>loại bỏ mùi hôi của hành và tỏi trên tay</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nhờ tính axit và mùi thơm tự nhiên.</t>
+    </r>
+  </si>
+  <si>
+    <t>Quả nào thường dùng giúp loại bỏ mùi hôi của hành tỏi trên tay???</t>
+  </si>
+  <si>
+    <t>Kiwi có nguồn gốc từ đâu ??</t>
+  </si>
+  <si>
+    <t>Mỹ</t>
+  </si>
+  <si>
+    <t>Ý</t>
+  </si>
+  <si>
+    <t>Trung Quốc</t>
+  </si>
+  <si>
+    <t>Kiwi có nguồn gốc từ Trung Quốc, sau đó được trồng phổ biến và phát triển mạnh ở New Zealand.</t>
+  </si>
+  <si>
+    <t>New Zealand</t>
+  </si>
+  <si>
+    <t>Loại trái nào giàu vitamin C nhất ??</t>
+  </si>
+  <si>
+    <t>Cam</t>
+  </si>
+  <si>
+    <t>Quýt</t>
+  </si>
+  <si>
+    <t>Ổi</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ổi là loại trái cây </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rất giàu vitamin C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, thậm chí nhiều hơn cả cam.</t>
+    </r>
+  </si>
+  <si>
+    <t>Nước mắm Phú Quốc nối tiếng vì điều gì ??</t>
+  </si>
+  <si>
+    <t>Làm từ Thịt tôm</t>
+  </si>
+  <si>
+    <t>Thơm ngon</t>
+  </si>
+  <si>
+    <t>Chưng từ vi cá</t>
+  </si>
+  <si>
+    <t>Đóng chai thủy tinh đẹp</t>
+  </si>
+  <si>
+    <t>Thơn ngon thì mới nổi chứ</t>
+  </si>
+  <si>
+    <t>Chợ nổi Cái Răng ở tỉnh nào ??</t>
+  </si>
+  <si>
+    <t>Vĩnh Long</t>
+  </si>
+  <si>
+    <t>Cần Thơ</t>
+  </si>
+  <si>
+    <t>Sóc Trăng</t>
+  </si>
+  <si>
+    <t>An Giang</t>
+  </si>
+  <si>
+    <t>Chợ nổi Cái Răng nằm ở thành phố Cần Thơ và là một trong những chợ nổi nổi tiếng nhất miền Tây Nam Bộ.</t>
+  </si>
+  <si>
+    <t>chonoi.jpg</t>
+  </si>
+  <si>
+    <t>G/Ắ/N/L/O/L</t>
+  </si>
+  <si>
+    <t>Lo lắng</t>
+  </si>
+  <si>
+    <t>B/Ố/C/T/Ứ/T</t>
+  </si>
+  <si>
+    <t>Bức tốc</t>
+  </si>
+  <si>
+    <t>C/Á/I/L/Ồ/C/Ó/N</t>
+  </si>
+  <si>
+    <t>Nồi cá lóc</t>
+  </si>
+  <si>
+    <t>C/Ọ/N/Ồ/L</t>
+  </si>
+  <si>
+    <t>Lọ cồn</t>
+  </si>
+  <si>
+    <t>C/U/C/H/ỉ/N/H</t>
+  </si>
+  <si>
+    <t>Chỉn chu</t>
+  </si>
+  <si>
+    <r>
+      <t>Chỉn chu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là từ dùng để chỉ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sự cẩn thận, gọn gàng và làm mọi thứ một cách kỹ lưỡng, tươm tất</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Huế - Đà Nẵng</t>
+  </si>
+  <si>
+    <t>Thẻ HTML nào sau dùng để tạo liên kết ??</t>
+  </si>
+  <si>
+    <t>&lt;img&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div&gt;</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trong HTML, thẻ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>&lt;a&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (anchor)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> được dùng để tạo </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>liên kết (hyperlink)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dẫn tới trang web khác, file khác hoặc một vị trí khác trong cùng trang.</t>
+    </r>
+  </si>
+  <si>
+    <t>Trong JavaScript, lệnh nào dùng để in ra console?</t>
+  </si>
+  <si>
+    <t>print()</t>
+  </si>
+  <si>
+    <t>echo()</t>
+  </si>
+  <si>
+    <t>console.log()</t>
+  </si>
+  <si>
+    <t>show()</t>
+  </si>
+  <si>
+    <r>
+      <t>console.log()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là lệnh trong JavaScript dùng để </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>in thông tin ra bảng Console của trình duyệt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Dev thường dùng nó để </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kiểm tra dữ liệu, debug và tìm lỗi trong code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>HTML là viết tắt của gì?</t>
+  </si>
+  <si>
+    <t>HyperText Markup Language</t>
+  </si>
+  <si>
+    <t>HighText Machine Language</t>
+  </si>
+  <si>
+    <t>Hyper Transfer Markup Language</t>
+  </si>
+  <si>
+    <t>Home Tool Markup Language</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HTML là </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HyperText Markup Language</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, ngôn ngữ dùng để </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tạo cấu trúc cho website</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> như tiêu đề, đoạn văn, hình ảnh, liên kết.</t>
+    </r>
+  </si>
+  <si>
+    <t>Này hỏi thật ấu Con gái nói không sao đâu nghĩa là gì ???</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -469,6 +1129,23 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -491,19 +1168,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -818,66 +1492,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6D20C5-F5C4-4FB0-8774-1BDFC45A7A57}">
-  <dimension ref="A1:Q51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="16384" width="8.88671875" style="5"/>
-  </cols>
+  <dimension ref="A1:Q42"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:17">
+      <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -908,16 +1579,16 @@
       <c r="L2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="2">
-        <v>5</v>
+      <c r="M2" s="1">
+        <v>7</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
-      <c r="P2" s="5" t="s">
+      <c r="P2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
@@ -943,15 +1614,15 @@
       <c r="L3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="2">
-        <v>5</v>
+      <c r="M3" s="1">
+        <v>7</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17">
       <c r="A4" s="1">
-        <f t="shared" ref="A4:A51" si="0">A3+1</f>
+        <f t="shared" ref="A4:A42" si="0">A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -983,16 +1654,16 @@
       <c r="L4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="2">
-        <v>5</v>
+      <c r="M4" s="1">
+        <v>4</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-      <c r="P4" s="5" t="s">
+      <c r="P4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1018,13 +1689,13 @@
       <c r="L5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="2">
-        <v>5</v>
+      <c r="M5" s="1">
+        <v>2</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1053,13 +1724,13 @@
       <c r="L6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="2">
-        <v>5</v>
+      <c r="M6" s="1">
+        <v>3</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1073,10 +1744,10 @@
       <c r="D7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7">
         <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -1085,22 +1756,22 @@
       <c r="J7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" t="s">
         <v>49</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="1">
         <v>5</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="P7" s="5" t="s">
+      <c r="P7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1114,19 +1785,19 @@
       <c r="D8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="L8" t="s">
         <v>44</v>
       </c>
-      <c r="M8" s="2">
-        <v>5</v>
+      <c r="M8" s="1">
+        <v>6</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-      <c r="P8" s="5" t="s">
+      <c r="P8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1140,10 +1811,10 @@
       <c r="D9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" t="s">
         <v>53</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -1152,19 +1823,19 @@
       <c r="J9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" t="s">
         <v>55</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M9" s="2">
-        <v>5</v>
+      <c r="M9" s="1">
+        <v>4</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1178,10 +1849,10 @@
       <c r="D10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" t="s">
         <v>58</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" t="s">
         <v>60</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -1190,19 +1861,19 @@
       <c r="J10" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" t="s">
         <v>63</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M10" s="2">
-        <v>5</v>
+      <c r="M10" s="1">
+        <v>3</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1213,34 +1884,34 @@
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" t="s">
         <v>106</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" t="s">
         <v>73</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" t="s">
         <v>75</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" t="s">
         <v>76</v>
       </c>
-      <c r="L11" s="5" t="s">
+      <c r="L11" t="s">
         <v>2</v>
       </c>
-      <c r="M11" s="2">
-        <v>10</v>
+      <c r="M11" s="1">
+        <v>7</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="5" t="s">
+      <c r="P11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1254,28 +1925,28 @@
       <c r="D12" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" t="s">
         <v>88</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" t="s">
         <v>87</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12" s="1">
         <v>5</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="5" t="s">
+      <c r="P12" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1289,25 +1960,25 @@
       <c r="D13" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" t="s">
         <v>92</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" t="s">
         <v>94</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13" s="1">
         <v>5</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1321,25 +1992,25 @@
       <c r="D14" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" t="s">
         <v>96</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" t="s">
         <v>98</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M14" s="1">
         <v>5</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1353,29 +2024,29 @@
       <c r="D15" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" t="s">
         <v>105</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" t="s">
         <v>101</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" t="s">
         <v>103</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="K15" t="s">
         <v>104</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M15" s="2">
+      <c r="M15" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1386,89 +2057,119 @@
       <c r="C16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" t="s">
         <v>81</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" t="s">
         <v>82</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" t="s">
         <v>83</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" t="s">
         <v>84</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" t="s">
         <v>85</v>
       </c>
-      <c r="L16" s="5" t="s">
+      <c r="L16" t="s">
         <v>2</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H17" s="5">
+      <c r="D17" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H17" t="s">
+        <v>134</v>
+      </c>
+      <c r="I17" t="s">
+        <v>135</v>
+      </c>
+      <c r="J17" t="s">
+        <v>136</v>
+      </c>
+      <c r="K17" t="s">
+        <v>137</v>
+      </c>
+      <c r="L17" t="s">
+        <v>2</v>
+      </c>
+      <c r="M17" s="1">
         <v>0</v>
       </c>
-      <c r="I17" s="5">
+      <c r="N17">
+        <v>10</v>
+      </c>
+      <c r="O17">
+        <v>10</v>
+      </c>
+      <c r="P17" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H18" t="s">
+        <v>140</v>
+      </c>
+      <c r="I18" t="s">
+        <v>141</v>
+      </c>
+      <c r="J18" t="s">
+        <v>142</v>
+      </c>
+      <c r="K18" t="s">
+        <v>143</v>
+      </c>
+      <c r="L18" t="s">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1">
         <v>0</v>
       </c>
-      <c r="J17" s="5">
-        <v>0</v>
-      </c>
-      <c r="K17" s="5">
-        <v>0</v>
-      </c>
-      <c r="L17" s="5">
-        <v>0</v>
-      </c>
-      <c r="M17" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="5">
-        <v>0</v>
-      </c>
-      <c r="I18" s="5">
-        <v>0</v>
-      </c>
-      <c r="J18" s="5">
-        <v>0</v>
-      </c>
-      <c r="K18" s="5">
-        <v>0</v>
-      </c>
-      <c r="L18" s="5">
-        <v>0</v>
-      </c>
-      <c r="M18" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N18">
+        <v>5</v>
+      </c>
+      <c r="O18">
+        <v>7</v>
+      </c>
+      <c r="P18" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1479,65 +2180,80 @@
       <c r="C19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" t="s">
         <v>127</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" t="s">
         <v>126</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" t="s">
         <v>128</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" t="s">
         <v>129</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" t="s">
         <v>132</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="K19" t="s">
         <v>130</v>
       </c>
-      <c r="L19" s="5" t="s">
+      <c r="L19" t="s">
         <v>1</v>
       </c>
-      <c r="M19" s="2">
+      <c r="M19" s="1">
         <v>10</v>
       </c>
-      <c r="P19" s="5" t="s">
+      <c r="P19" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H20" s="5">
+      <c r="D20" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H20" t="s">
+        <v>162</v>
+      </c>
+      <c r="I20" t="s">
+        <v>163</v>
+      </c>
+      <c r="J20" t="s">
+        <v>222</v>
+      </c>
+      <c r="K20" t="s">
+        <v>164</v>
+      </c>
+      <c r="L20" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="1">
         <v>0</v>
       </c>
-      <c r="I20" s="5">
-        <v>0</v>
-      </c>
-      <c r="J20" s="5">
-        <v>0</v>
-      </c>
-      <c r="K20" s="5">
-        <v>0</v>
-      </c>
-      <c r="L20" s="5">
-        <v>0</v>
-      </c>
-      <c r="M20" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N20">
+        <v>5</v>
+      </c>
+      <c r="O20">
+        <v>9</v>
+      </c>
+      <c r="P20" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1548,26 +2264,35 @@
       <c r="C21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="5">
-        <v>0</v>
-      </c>
-      <c r="I21" s="5">
-        <v>0</v>
-      </c>
-      <c r="J21" s="5">
-        <v>0</v>
-      </c>
-      <c r="K21" s="5">
-        <v>0</v>
-      </c>
-      <c r="L21" s="5">
-        <v>0</v>
-      </c>
-      <c r="M21" s="2">
+      <c r="D21" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I21" t="s">
+        <v>174</v>
+      </c>
+      <c r="J21" t="s">
+        <v>175</v>
+      </c>
+      <c r="K21" t="s">
+        <v>176</v>
+      </c>
+      <c r="L21" t="s">
+        <v>2</v>
+      </c>
+      <c r="M21" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P21" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1576,28 +2301,19 @@
         <v>18</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H22" s="5">
-        <v>0</v>
-      </c>
-      <c r="I22" s="5">
-        <v>0</v>
-      </c>
-      <c r="J22" s="5">
-        <v>0</v>
-      </c>
-      <c r="K22" s="5">
-        <v>0</v>
-      </c>
-      <c r="L22" s="5">
-        <v>0</v>
-      </c>
-      <c r="M22" s="2">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L22" t="s">
+        <v>212</v>
+      </c>
+      <c r="M22" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1608,38 +2324,38 @@
       <c r="C23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" t="s">
         <v>107</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" t="s">
         <v>113</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" t="s">
         <v>117</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="I23" t="s">
         <v>116</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="J23" t="s">
         <v>115</v>
       </c>
-      <c r="K23" s="5" t="s">
+      <c r="K23" t="s">
         <v>114</v>
       </c>
-      <c r="L23" s="5" t="s">
+      <c r="L23" t="s">
         <v>1</v>
       </c>
-      <c r="M23" s="2">
+      <c r="M23" s="1">
         <v>10</v>
       </c>
-      <c r="P23" s="5" t="s">
+      <c r="P23" t="s">
         <v>119</v>
       </c>
-      <c r="Q23" s="5" t="s">
+      <c r="Q23" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1650,26 +2366,35 @@
       <c r="C24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H24" s="5">
-        <v>0</v>
-      </c>
-      <c r="I24" s="5">
-        <v>0</v>
-      </c>
-      <c r="J24" s="5">
-        <v>0</v>
-      </c>
-      <c r="K24" s="5">
-        <v>0</v>
-      </c>
-      <c r="L24" s="5">
-        <v>0</v>
-      </c>
-      <c r="M24" s="2">
+      <c r="D24" t="s">
+        <v>153</v>
+      </c>
+      <c r="F24" t="s">
+        <v>147</v>
+      </c>
+      <c r="H24" t="s">
+        <v>148</v>
+      </c>
+      <c r="I24" t="s">
+        <v>149</v>
+      </c>
+      <c r="J24" t="s">
+        <v>150</v>
+      </c>
+      <c r="K24" t="s">
+        <v>151</v>
+      </c>
+      <c r="L24" t="s">
+        <v>2</v>
+      </c>
+      <c r="M24" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1680,86 +2405,104 @@
       <c r="C25" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="5">
+      <c r="D25" t="s">
+        <v>167</v>
+      </c>
+      <c r="H25" t="s">
+        <v>169</v>
+      </c>
+      <c r="I25" t="s">
+        <v>170</v>
+      </c>
+      <c r="J25" t="s">
+        <v>168</v>
+      </c>
+      <c r="K25" t="s">
+        <v>171</v>
+      </c>
+      <c r="L25" t="s">
+        <v>3</v>
+      </c>
+      <c r="M25" s="1">
+        <v>10</v>
+      </c>
+      <c r="P25" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" t="s">
+        <v>213</v>
+      </c>
+      <c r="L26" t="s">
+        <v>214</v>
+      </c>
+      <c r="M26" s="1">
         <v>0</v>
       </c>
-      <c r="I25" s="5">
+      <c r="N26">
+        <v>5</v>
+      </c>
+      <c r="O26">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="1">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>223</v>
+      </c>
+      <c r="H27" t="s">
+        <v>224</v>
+      </c>
+      <c r="I27" t="s">
+        <v>225</v>
+      </c>
+      <c r="J27" t="s">
+        <v>226</v>
+      </c>
+      <c r="K27" t="s">
+        <v>227</v>
+      </c>
+      <c r="L27" t="s">
+        <v>2</v>
+      </c>
+      <c r="M27" s="1">
         <v>0</v>
       </c>
-      <c r="J25" s="5">
-        <v>0</v>
-      </c>
-      <c r="K25" s="5">
-        <v>0</v>
-      </c>
-      <c r="L25" s="5">
-        <v>0</v>
-      </c>
-      <c r="M25" s="2">
+      <c r="N27">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H26" s="5">
-        <v>0</v>
-      </c>
-      <c r="I26" s="5">
-        <v>0</v>
-      </c>
-      <c r="J26" s="5">
-        <v>0</v>
-      </c>
-      <c r="K26" s="5">
-        <v>0</v>
-      </c>
-      <c r="L26" s="5">
-        <v>0</v>
-      </c>
-      <c r="M26" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H27" s="5">
-        <v>0</v>
-      </c>
-      <c r="I27" s="5">
-        <v>0</v>
-      </c>
-      <c r="J27" s="5">
-        <v>0</v>
-      </c>
-      <c r="K27" s="5">
-        <v>0</v>
-      </c>
-      <c r="L27" s="5">
-        <v>0</v>
-      </c>
-      <c r="M27" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O27">
+        <v>6</v>
+      </c>
+      <c r="P27" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -1770,26 +2513,35 @@
       <c r="C28" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H28" s="5">
-        <v>0</v>
-      </c>
-      <c r="I28" s="5">
-        <v>0</v>
-      </c>
-      <c r="J28" s="5">
-        <v>0</v>
-      </c>
-      <c r="K28" s="5">
-        <v>0</v>
-      </c>
-      <c r="L28" s="5">
-        <v>0</v>
-      </c>
-      <c r="M28" s="2">
+      <c r="D28" t="s">
+        <v>155</v>
+      </c>
+      <c r="F28" t="s">
+        <v>154</v>
+      </c>
+      <c r="H28" t="s">
+        <v>158</v>
+      </c>
+      <c r="I28" t="s">
+        <v>157</v>
+      </c>
+      <c r="J28" t="s">
+        <v>159</v>
+      </c>
+      <c r="K28" t="s">
+        <v>156</v>
+      </c>
+      <c r="L28" t="s">
+        <v>4</v>
+      </c>
+      <c r="M28" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P28" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1800,26 +2552,32 @@
       <c r="C29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H29" s="5">
-        <v>0</v>
-      </c>
-      <c r="I29" s="5">
-        <v>0</v>
-      </c>
-      <c r="J29" s="5">
-        <v>0</v>
-      </c>
-      <c r="K29" s="5">
-        <v>0</v>
-      </c>
-      <c r="L29" s="5">
-        <v>0</v>
-      </c>
-      <c r="M29" s="2">
+      <c r="D29" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" t="s">
+        <v>125</v>
+      </c>
+      <c r="H29" t="s">
+        <v>109</v>
+      </c>
+      <c r="I29" t="s">
+        <v>110</v>
+      </c>
+      <c r="J29" t="s">
+        <v>111</v>
+      </c>
+      <c r="K29" t="s">
+        <v>112</v>
+      </c>
+      <c r="L29" t="s">
+        <v>2</v>
+      </c>
+      <c r="M29" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -1828,34 +2586,19 @@
         <v>18</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="M30" s="2">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
+        <v>215</v>
+      </c>
+      <c r="L30" t="s">
+        <v>216</v>
+      </c>
+      <c r="M30" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1866,26 +2609,35 @@
       <c r="C31" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="5">
-        <v>0</v>
-      </c>
-      <c r="I31" s="5">
-        <v>0</v>
-      </c>
-      <c r="J31" s="5">
-        <v>0</v>
-      </c>
-      <c r="K31" s="5">
-        <v>0</v>
-      </c>
-      <c r="L31" s="5">
-        <v>0</v>
-      </c>
-      <c r="M31" s="2">
+      <c r="D31" t="s">
+        <v>204</v>
+      </c>
+      <c r="H31" t="s">
+        <v>206</v>
+      </c>
+      <c r="I31" t="s">
+        <v>207</v>
+      </c>
+      <c r="J31" t="s">
+        <v>205</v>
+      </c>
+      <c r="K31" t="s">
+        <v>208</v>
+      </c>
+      <c r="L31" t="s">
+        <v>1</v>
+      </c>
+      <c r="M31" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P31" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -1896,86 +2648,101 @@
       <c r="C32" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="5">
+      <c r="D32" t="s">
+        <v>186</v>
+      </c>
+      <c r="H32" t="s">
+        <v>181</v>
+      </c>
+      <c r="I32" t="s">
+        <v>182</v>
+      </c>
+      <c r="J32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K32" t="s">
+        <v>184</v>
+      </c>
+      <c r="L32" t="s">
+        <v>2</v>
+      </c>
+      <c r="M32" s="1">
+        <v>10</v>
+      </c>
+      <c r="P32" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="1">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" t="s">
+        <v>217</v>
+      </c>
+      <c r="L33" t="s">
+        <v>218</v>
+      </c>
+      <c r="M33" s="1">
         <v>0</v>
       </c>
-      <c r="I32" s="5">
+      <c r="N33">
+        <v>8</v>
+      </c>
+      <c r="O33">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="1">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>229</v>
+      </c>
+      <c r="H34" t="s">
+        <v>230</v>
+      </c>
+      <c r="I34" t="s">
+        <v>231</v>
+      </c>
+      <c r="J34" t="s">
+        <v>232</v>
+      </c>
+      <c r="K34" t="s">
+        <v>233</v>
+      </c>
+      <c r="L34" t="s">
+        <v>3</v>
+      </c>
+      <c r="M34" s="1">
         <v>0</v>
       </c>
-      <c r="J32" s="5">
-        <v>0</v>
-      </c>
-      <c r="K32" s="5">
-        <v>0</v>
-      </c>
-      <c r="L32" s="5">
-        <v>0</v>
-      </c>
-      <c r="M32" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H33" s="5">
-        <v>0</v>
-      </c>
-      <c r="I33" s="5">
-        <v>0</v>
-      </c>
-      <c r="J33" s="5">
-        <v>0</v>
-      </c>
-      <c r="K33" s="5">
-        <v>0</v>
-      </c>
-      <c r="L33" s="5">
-        <v>0</v>
-      </c>
-      <c r="M33" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H34" s="5">
-        <v>0</v>
-      </c>
-      <c r="I34" s="5">
-        <v>0</v>
-      </c>
-      <c r="J34" s="5">
-        <v>0</v>
-      </c>
-      <c r="K34" s="5">
-        <v>0</v>
-      </c>
-      <c r="L34" s="5">
-        <v>0</v>
-      </c>
-      <c r="M34" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N34">
+        <v>9</v>
+      </c>
+      <c r="O34">
+        <v>5</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -1986,176 +2753,227 @@
       <c r="C35" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H35" s="5">
+      <c r="D35" t="s">
+        <v>198</v>
+      </c>
+      <c r="H35" t="s">
+        <v>199</v>
+      </c>
+      <c r="I35" t="s">
+        <v>200</v>
+      </c>
+      <c r="J35" t="s">
+        <v>201</v>
+      </c>
+      <c r="K35" t="s">
+        <v>202</v>
+      </c>
+      <c r="L35" t="s">
+        <v>2</v>
+      </c>
+      <c r="M35" s="1">
+        <v>10</v>
+      </c>
+      <c r="P35" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="1">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>187</v>
+      </c>
+      <c r="H36" t="s">
+        <v>188</v>
+      </c>
+      <c r="I36" t="s">
+        <v>192</v>
+      </c>
+      <c r="J36" t="s">
+        <v>189</v>
+      </c>
+      <c r="K36" t="s">
+        <v>190</v>
+      </c>
+      <c r="L36" t="s">
+        <v>4</v>
+      </c>
+      <c r="M36" s="1">
         <v>0</v>
       </c>
-      <c r="I35" s="5">
+      <c r="N36">
+        <v>6</v>
+      </c>
+      <c r="O36">
+        <v>12</v>
+      </c>
+      <c r="P36" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="1">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="s">
+        <v>235</v>
+      </c>
+      <c r="H37" t="s">
+        <v>236</v>
+      </c>
+      <c r="I37" t="s">
+        <v>237</v>
+      </c>
+      <c r="J37" t="s">
+        <v>238</v>
+      </c>
+      <c r="K37" t="s">
+        <v>239</v>
+      </c>
+      <c r="L37" t="s">
+        <v>1</v>
+      </c>
+      <c r="M37" s="1">
         <v>0</v>
       </c>
-      <c r="J35" s="5">
+      <c r="N37">
+        <v>5</v>
+      </c>
+      <c r="O37">
+        <v>8</v>
+      </c>
+      <c r="P37" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="1">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" t="s">
+        <v>219</v>
+      </c>
+      <c r="L38" t="s">
+        <v>220</v>
+      </c>
+      <c r="M38" s="1">
         <v>0</v>
       </c>
-      <c r="K35" s="5">
+      <c r="N38">
+        <v>4</v>
+      </c>
+      <c r="O38">
+        <v>8</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="1">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" t="s">
+        <v>33</v>
+      </c>
+      <c r="I39" t="s">
+        <v>34</v>
+      </c>
+      <c r="J39" t="s">
+        <v>35</v>
+      </c>
+      <c r="K39" t="s">
+        <v>36</v>
+      </c>
+      <c r="L39" t="s">
+        <v>3</v>
+      </c>
+      <c r="M39" s="1">
         <v>0</v>
       </c>
-      <c r="L35" s="5">
+      <c r="N39">
+        <v>8</v>
+      </c>
+      <c r="O39">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="1">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>193</v>
+      </c>
+      <c r="H40" t="s">
+        <v>194</v>
+      </c>
+      <c r="I40" t="s">
+        <v>195</v>
+      </c>
+      <c r="J40" t="s">
+        <v>196</v>
+      </c>
+      <c r="K40" t="s">
+        <v>182</v>
+      </c>
+      <c r="L40" t="s">
+        <v>3</v>
+      </c>
+      <c r="M40" s="1">
         <v>0</v>
       </c>
-      <c r="M35" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H36" s="5">
-        <v>0</v>
-      </c>
-      <c r="I36" s="5">
-        <v>0</v>
-      </c>
-      <c r="J36" s="5">
-        <v>0</v>
-      </c>
-      <c r="K36" s="5">
-        <v>0</v>
-      </c>
-      <c r="L36" s="5">
-        <v>0</v>
-      </c>
-      <c r="M36" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H37" s="5">
-        <v>0</v>
-      </c>
-      <c r="I37" s="5">
-        <v>0</v>
-      </c>
-      <c r="J37" s="5">
-        <v>0</v>
-      </c>
-      <c r="K37" s="5">
-        <v>0</v>
-      </c>
-      <c r="L37" s="5">
-        <v>0</v>
-      </c>
-      <c r="M37" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H38" s="5">
-        <v>0</v>
-      </c>
-      <c r="I38" s="5">
-        <v>0</v>
-      </c>
-      <c r="J38" s="5">
-        <v>0</v>
-      </c>
-      <c r="K38" s="5">
-        <v>0</v>
-      </c>
-      <c r="L38" s="5">
-        <v>0</v>
-      </c>
-      <c r="M38" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H39" s="5">
-        <v>0</v>
-      </c>
-      <c r="I39" s="5">
-        <v>0</v>
-      </c>
-      <c r="J39" s="5">
-        <v>0</v>
-      </c>
-      <c r="K39" s="5">
-        <v>0</v>
-      </c>
-      <c r="L39" s="5">
-        <v>0</v>
-      </c>
-      <c r="M39" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H40" s="5">
-        <v>0</v>
-      </c>
-      <c r="I40" s="5">
-        <v>0</v>
-      </c>
-      <c r="J40" s="5">
-        <v>0</v>
-      </c>
-      <c r="K40" s="5">
-        <v>0</v>
-      </c>
-      <c r="L40" s="5">
-        <v>0</v>
-      </c>
-      <c r="M40" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N40">
+        <v>7</v>
+      </c>
+      <c r="O40">
+        <v>12</v>
+      </c>
+      <c r="P40" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -2166,26 +2984,35 @@
       <c r="C41" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H41" s="5">
+      <c r="D41" t="s">
+        <v>67</v>
+      </c>
+      <c r="H41" t="s">
+        <v>68</v>
+      </c>
+      <c r="I41" t="s">
+        <v>69</v>
+      </c>
+      <c r="J41" t="s">
+        <v>70</v>
+      </c>
+      <c r="K41" t="s">
+        <v>71</v>
+      </c>
+      <c r="L41" t="s">
+        <v>4</v>
+      </c>
+      <c r="M41" s="1">
         <v>0</v>
       </c>
-      <c r="I41" s="5">
-        <v>0</v>
-      </c>
-      <c r="J41" s="5">
-        <v>0</v>
-      </c>
-      <c r="K41" s="5">
-        <v>0</v>
-      </c>
-      <c r="L41" s="5">
-        <v>0</v>
-      </c>
-      <c r="M41" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N41">
+        <v>10</v>
+      </c>
+      <c r="O41">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -2196,314 +3023,30 @@
       <c r="C42" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H42" s="5">
+      <c r="D42" t="s">
+        <v>120</v>
+      </c>
+      <c r="H42" t="s">
+        <v>121</v>
+      </c>
+      <c r="I42" t="s">
+        <v>122</v>
+      </c>
+      <c r="J42" t="s">
+        <v>123</v>
+      </c>
+      <c r="K42" t="s">
+        <v>124</v>
+      </c>
+      <c r="M42" s="1">
         <v>0</v>
       </c>
-      <c r="I42" s="5">
-        <v>0</v>
-      </c>
-      <c r="J42" s="5">
-        <v>0</v>
-      </c>
-      <c r="K42" s="5">
-        <v>0</v>
-      </c>
-      <c r="L42" s="5">
-        <v>0</v>
-      </c>
-      <c r="M42" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L43" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="2">
-        <v>0</v>
-      </c>
-      <c r="N43" s="5">
-        <v>15</v>
-      </c>
-      <c r="O43" s="5">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H44" s="5">
-        <v>0</v>
-      </c>
-      <c r="I44" s="5">
-        <v>0</v>
-      </c>
-      <c r="J44" s="5">
-        <v>0</v>
-      </c>
-      <c r="K44" s="5">
-        <v>0</v>
-      </c>
-      <c r="L44" s="5">
-        <v>0</v>
-      </c>
-      <c r="M44" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K45" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="L45" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="M45" s="2">
-        <v>0</v>
-      </c>
-      <c r="N45" s="5">
-        <v>10</v>
-      </c>
-      <c r="O45" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H46" s="5">
-        <v>0</v>
-      </c>
-      <c r="I46" s="5">
-        <v>0</v>
-      </c>
-      <c r="J46" s="5">
-        <v>0</v>
-      </c>
-      <c r="K46" s="5">
-        <v>0</v>
-      </c>
-      <c r="L46" s="5">
-        <v>0</v>
-      </c>
-      <c r="M46" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H47" s="5">
-        <v>0</v>
-      </c>
-      <c r="I47" s="5">
-        <v>0</v>
-      </c>
-      <c r="J47" s="5">
-        <v>0</v>
-      </c>
-      <c r="K47" s="5">
-        <v>0</v>
-      </c>
-      <c r="L47" s="5">
-        <v>0</v>
-      </c>
-      <c r="M47" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H48" s="5">
-        <v>0</v>
-      </c>
-      <c r="I48" s="5">
-        <v>0</v>
-      </c>
-      <c r="J48" s="5">
-        <v>0</v>
-      </c>
-      <c r="K48" s="5">
-        <v>0</v>
-      </c>
-      <c r="L48" s="5">
-        <v>0</v>
-      </c>
-      <c r="M48" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H49" s="5">
-        <v>0</v>
-      </c>
-      <c r="I49" s="5">
-        <v>0</v>
-      </c>
-      <c r="J49" s="5">
-        <v>0</v>
-      </c>
-      <c r="K49" s="5">
-        <v>0</v>
-      </c>
-      <c r="L49" s="5">
-        <v>0</v>
-      </c>
-      <c r="M49" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H50" s="5">
-        <v>0</v>
-      </c>
-      <c r="I50" s="5">
-        <v>0</v>
-      </c>
-      <c r="J50" s="5">
-        <v>0</v>
-      </c>
-      <c r="K50" s="5">
-        <v>0</v>
-      </c>
-      <c r="L50" s="5">
-        <v>0</v>
-      </c>
-      <c r="M50" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="H51" t="s">
-        <v>121</v>
-      </c>
-      <c r="I51" t="s">
-        <v>122</v>
-      </c>
-      <c r="J51" t="s">
-        <v>123</v>
-      </c>
-      <c r="K51" t="s">
-        <v>124</v>
-      </c>
-      <c r="M51" s="2">
-        <v>0</v>
+      <c r="P42" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/question/Question.xlsx
+++ b/question/Question.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\file_luu_tru\du_an\minigame\question\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB780B9-045B-480E-A6D0-FD42C5200A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0AA3C1-FEAF-4B3A-B37C-F075C341F431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{13D47C2E-6DA5-4663-B107-8F3B884F698D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="262">
   <si>
     <t>question</t>
   </si>
@@ -1108,6 +1108,66 @@
   </si>
   <si>
     <t>Này hỏi thật ấu Con gái nói không sao đâu nghĩa là gì ???</t>
+  </si>
+  <si>
+    <t>Tứ bất tử trong văn hóa không bao gồm ai ??</t>
+  </si>
+  <si>
+    <t>Sơn tinh</t>
+  </si>
+  <si>
+    <t>Lý Thường Kiệt</t>
+  </si>
+  <si>
+    <t>Chử Đồng Tử</t>
+  </si>
+  <si>
+    <t>Thánh Gióng</t>
+  </si>
+  <si>
+    <t>Tứ bất tử là bốn vị thánh được dân gian Việt Nam tôn thờ, tượng trưng cho những giá trị tinh thần, khát vọng trường tồn, và bản sắc văn hóa dân tộc</t>
+  </si>
+  <si>
+    <t>p/d/ọ/d/n/ẹ</t>
+  </si>
+  <si>
+    <t>dọn dẹp</t>
+  </si>
+  <si>
+    <t>ireland.jpg</t>
+  </si>
+  <si>
+    <t>đây là con vật đại diện nước nào</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>Thụy Sĩ</t>
+  </si>
+  <si>
+    <t>Hà Lan</t>
+  </si>
+  <si>
+    <t>Thụy Điển</t>
+  </si>
+  <si>
+    <t>Red Deer (hươu đỏ) là loài hươu lớn và nổi tiếng ở Ireland, thường được xem là biểu tượng động vật đặc trưng của quốc gia này trong tự nhiên và văn hóa.</t>
+  </si>
+  <si>
+    <t>thonhiki.png</t>
+  </si>
+  <si>
+    <t>Đây là bản đồ quốc gia nào</t>
+  </si>
+  <si>
+    <t>Thổ Nhĩ Kỳ</t>
+  </si>
+  <si>
+    <t>Triều Tiên</t>
+  </si>
+  <si>
+    <t>Iran</t>
   </si>
 </sst>
 </file>
@@ -1168,7 +1228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1178,6 +1238,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1492,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6D20C5-F5C4-4FB0-8774-1BDFC45A7A57}">
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1622,7 +1683,7 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="1">
-        <f t="shared" ref="A4:A42" si="0">A3+1</f>
+        <f t="shared" ref="A4:A47" si="0">A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -3018,30 +3079,162 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>242</v>
+      </c>
+      <c r="H42" t="s">
+        <v>243</v>
+      </c>
+      <c r="I42" t="s">
+        <v>244</v>
+      </c>
+      <c r="J42" t="s">
+        <v>245</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M42" s="1">
+        <v>7</v>
+      </c>
+      <c r="P42" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="1">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" t="s">
+        <v>248</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="M43" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="1">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s">
+        <v>251</v>
+      </c>
+      <c r="E44" t="s">
+        <v>250</v>
+      </c>
+      <c r="H44" t="s">
+        <v>252</v>
+      </c>
+      <c r="I44" t="s">
+        <v>253</v>
+      </c>
+      <c r="J44" t="s">
+        <v>254</v>
+      </c>
+      <c r="K44" t="s">
+        <v>255</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M44" s="1">
+        <v>5</v>
+      </c>
+      <c r="P44" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="1">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" t="s">
+        <v>258</v>
+      </c>
+      <c r="E45" t="s">
+        <v>257</v>
+      </c>
+      <c r="H45" t="s">
+        <v>188</v>
+      </c>
+      <c r="I45" t="s">
+        <v>260</v>
+      </c>
+      <c r="J45" t="s">
+        <v>261</v>
+      </c>
+      <c r="K45" t="s">
+        <v>259</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="1">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="C46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
         <v>120</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H46" t="s">
         <v>121</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I46" t="s">
         <v>122</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J46" t="s">
         <v>123</v>
       </c>
-      <c r="K42" t="s">
+      <c r="K46" t="s">
         <v>124</v>
       </c>
-      <c r="M42" s="1">
-        <v>0</v>
-      </c>
-      <c r="P42" t="s">
+      <c r="M46" s="1">
+        <v>1</v>
+      </c>
+      <c r="P46" t="s">
         <v>241</v>
       </c>
     </row>
